--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,117 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120111538</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102217</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>350184</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434268</v>
+      </c>
+      <c r="S4" t="n">
+        <v>62</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Arlid 1:4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839368</v>
+        <v>119839375</v>
       </c>
       <c r="B2" t="n">
-        <v>58138</v>
+        <v>105564</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839375</v>
+        <v>119839368</v>
       </c>
       <c r="B3" t="n">
-        <v>105564</v>
+        <v>58138</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839375</v>
+        <v>119839368</v>
       </c>
       <c r="B2" t="n">
-        <v>105564</v>
+        <v>58138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839368</v>
+        <v>119839375</v>
       </c>
       <c r="B3" t="n">
-        <v>58138</v>
+        <v>105564</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,32 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839375</v>
+        <v>119839368</v>
       </c>
       <c r="B2" t="n">
-        <v>105564</v>
+        <v>58148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839368</v>
+        <v>119839375</v>
       </c>
       <c r="B3" t="n">
-        <v>58138</v>
+        <v>105588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,32 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>120111538</v>
       </c>
       <c r="B4" t="n">
-        <v>102217</v>
+        <v>102240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839368</v>
+        <v>119839375</v>
       </c>
       <c r="B2" t="n">
-        <v>58148</v>
+        <v>105588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -787,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839375</v>
+        <v>119839368</v>
       </c>
       <c r="B3" t="n">
-        <v>105588</v>
+        <v>58148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +798,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,118 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125156072</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56471</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>350184</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434268</v>
+      </c>
+      <c r="S5" t="n">
+        <v>62</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Arlid 1:4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>125156072</v>
       </c>
       <c r="B5" t="n">
-        <v>56471</v>
+        <v>56585</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1012,12 +1012,7 @@
         <v>125156072</v>
       </c>
       <c r="B5" t="n">
-        <v>56585</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,6 +1114,112 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132563310</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104606</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Arlid 1:4, skogen Ö om norra hagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>350195</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434176</v>
+      </c>
+      <c r="S6" t="n">
+        <v>36</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Arlid 1:4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104606</v>
+        <v>104614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104614</v>
+        <v>104625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104625</v>
+        <v>104626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104626</v>
+        <v>104627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104627</v>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>132563310</v>
       </c>
       <c r="B6" t="n">
-        <v>104628</v>
+        <v>104629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -675,43 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839375</v>
+        <v>119839368</v>
       </c>
       <c r="B2" t="n">
-        <v>105588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -786,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839368</v>
+        <v>125156072</v>
       </c>
       <c r="B3" t="n">
-        <v>58148</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +818,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arlid 1:4, hygget i NO, norr om vägen, Vg</t>
+          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350179</v>
+        <v>350184</v>
       </c>
       <c r="R3" t="n">
-        <v>6434353</v>
+        <v>6434268</v>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +878,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Götmark, Espen Quinto-Ashman</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -898,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111538</v>
+        <v>119839375</v>
       </c>
       <c r="B4" t="n">
-        <v>102240</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,17 +924,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
+          <t>Arlid 1:4, hygget i NO, norr om vägen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350184</v>
+        <v>350179</v>
       </c>
       <c r="R4" t="n">
-        <v>6434268</v>
+        <v>6434353</v>
       </c>
       <c r="S4" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +984,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Elin Götmark, Espen Quinto-Ashman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1009,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125156072</v>
+        <v>132563310</v>
       </c>
       <c r="B5" t="n">
-        <v>56586</v>
+        <v>104707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,42 +1006,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
+          <t>Arlid 1:4, skogen Ö om norra hagen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350184</v>
+        <v>350195</v>
       </c>
       <c r="R5" t="n">
-        <v>6434268</v>
+        <v>6434176</v>
       </c>
       <c r="S5" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132563310</v>
+        <v>120111538</v>
       </c>
       <c r="B6" t="n">
-        <v>104642</v>
+        <v>103403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>223246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,17 +1136,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arlid 1:4, skogen Ö om norra hagen, Vg</t>
+          <t>Arlid 1:4, hygget i NO, s om vägen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>350195</v>
+        <v>350184</v>
       </c>
       <c r="R6" t="n">
-        <v>6434176</v>
+        <v>6434268</v>
       </c>
       <c r="S6" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,12 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 10017-2022 artfynd.xlsx
+++ b/artfynd/A 10017-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
           <t>Arlid 1:4</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Arlid 1:4</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125156072</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
           <t>Arlid 1:4</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Arlid 1:4</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132563310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
           <t>Arlid 1:4</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120111538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>